--- a/Historico_Eventos_Automatizado.xlsx
+++ b/Historico_Eventos_Automatizado.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,14 +48,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,14 +441,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="168" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
@@ -442,6 +462,2115 @@
       <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Este archivo constituye la base histórica de indicadores macroeconómicos. Datos extraídos de investing.com, e intenta recopilar los eventos o indicadores publicados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>CLFestividad</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Chile - Primer Grito de Independencia</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Festividad</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Declaraciones de política monetaria del BoJ</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Decisión de tipos de interés</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Ventas minoristas subyacentes (Mensual) (Ago)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>-0,2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Ventas minoristas subyacentes (Anual) (Ago)</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Ventas minoristas (Anual) (Ago)</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Ventas minoristas (Mensual) (Ago)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>-0,2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>IPP de Alemania (Mensual) (Ago)</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>IPP de Alemania (Anual) (Ago)</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Rueda de prensa del Banco de Japón</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Cuenta corriente en la zona euro  (Jul)</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>27,6B</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>30,7B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Cuenta corriente (no ajustada estacionalmente) en la zona euro  (Jul)</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>36,5B</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Producción del sector de la construcción (Mensual) (Jul)</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>0,00%</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Inversión extranjera directa  (Ago)</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>-5,30%</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Cuenta corriente de Portugal  (Jul)</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>-1,009B</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Reunión del Eurogrupo</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Reuniones del Ecofin</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Comparecencia de Lagarde, presidenta del BCE</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Reserva de divisas, USD</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>780,78B</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Evolución de los préstamos bancarios</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>19,1%</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Crecimiento de los depósitos</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>17,8%</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Índice de precios de viviendas nuevas (Mensual)</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>-0,1%</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Demanda agregada (Trimestral) (2T)</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>1,70%</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Gasto privado (Trimestral) (2T)</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>0,90%</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Gasto privado (Anual) (2T)</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>2,10%</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Demanda agregada (Anual) (2T)</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>5,80%</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Producción industrial (Anual) (Ago)</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Índice de producción industrial (Mensual) (Ago)</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Producción manufacturera (Mensual) (Ago)</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>-0,3%</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Tasa de utilización de la capacidad instalada  (Ago)</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>76,3%</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>76,4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Balance presupuestario  (Ago)</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>1.990M</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Comparecencia de Bowman, miembro del FOMC</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Índice principal de EE.UU. (Mensual) (Ago)</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>-0,1%</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Discurso de Schmid, de la Fed</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Número de plataformas petrolíferas, Baker Hughes</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Recuento de yacimientos activos en EE.UU. de Baker Hughes</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Balanza comercial  (Ago)</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>2.055M</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Posiciones netas especulativas en el GBP de la CFTC</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Posiciones netas especulativas en el S&amp;P 500 de la CFTC</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Posiciones netas especulativas en el Nasdaq 100 de la CFTC</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Posiciones netas especulativas en el oro de la CFTC</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Posiciones netas especulativas en el petróleo de la CFTC</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Posiciones netas especulativas del aluminio del CFTC</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Posiciones netas especulativas en el cobre de la CFTC</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Posiciones netas especulativas en la plata de la CFTC</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Posiciones netas especulativas del gas natural del CFTC</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Posiciones netas especulativas sobre trigo del CFTC</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Posiciones netas especulativas sobre maíz del CFTC</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Posiciones netas especulativas sobre soja del CFTC</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Posiciones netas especulativas en el CAD de la CFTC</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Posiciones netas especulativas en el MXN de la CFTC</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Posiciones netas especulativas en el CHF de la CFTC</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Posiciones netas especulativas en el AUD de la CFTC</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Posiciones netas especulativas del BRL en la CFTC</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Posiciones netas especulativas en el JPY de la CFTC</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Posiciones netas especulativas en el NZD de la CFTC</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Posiciones netas especulativas en el EUR de la CFTC</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
